--- a/diseases/d090/2026-2029.xlsx
+++ b/diseases/d090/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2335,9 +2323,6 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="inlineStr">

--- a/diseases/d090/2026-2029.xlsx
+++ b/diseases/d090/2026-2029.xlsx
@@ -2643,6 +2643,396 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D090</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>babesiosis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Babesiosis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D090</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Babesiosis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>巴贝西虫病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BABESIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BABESIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D090</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>babesiosis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Babesiosis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D090</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Babesiosis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>巴贝西虫病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BABESIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BABESIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Babesiosis</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary babesiosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BABESIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2676,7 +3066,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2759,7 +3149,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2769,7 +3159,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2789,7 +3179,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
